--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/OKLAHOMA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/OKLAHOMA_2010.xlsx
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C85">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C127">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C155">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C425">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C461">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C462">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C696">
